--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>126958386</v>
       </c>
       <c r="B6" t="n">
-        <v>91652</v>
+        <v>91726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>127014487</v>
       </c>
       <c r="B8" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>126958386</v>
       </c>
       <c r="B6" t="n">
-        <v>91726</v>
+        <v>91732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>127014487</v>
       </c>
       <c r="B8" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>126958386</v>
       </c>
       <c r="B6" t="n">
-        <v>91732</v>
+        <v>91733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>126958386</v>
       </c>
       <c r="B6" t="n">
-        <v>91733</v>
+        <v>91737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>127014487</v>
       </c>
       <c r="B8" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>126958386</v>
       </c>
       <c r="B6" t="n">
-        <v>91737</v>
+        <v>91739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>127014487</v>
       </c>
       <c r="B8" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>126958386</v>
       </c>
       <c r="B6" t="n">
-        <v>91739</v>
+        <v>91726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>127014487</v>
       </c>
       <c r="B8" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30405-2025 artfynd.xlsx
+++ b/artfynd/A 30405-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126958529</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126957597</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>126958987</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>126957938</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>126958386</v>
       </c>
       <c r="B6" t="n">
-        <v>91726</v>
+        <v>91739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>126958749</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>127014487</v>
       </c>
       <c r="B8" t="n">
-        <v>75135</v>
+        <v>75144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
